--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(6).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(6).xlsx
@@ -409,7 +409,25 @@
     <t>只见座椅上的男人呼吸一紧，干涩的喉咙里随即滚出一声浑浊的闷咳，突然的惊厥让他猛地吸入一口辛辣的空气，若非克拉克及时把瓶子移开，流清鼻涕的症状大概会一直持续到他从这场梦中醒来。</t>
   </si>
   <si>
-    <t>loadScript(终局（下）_84, 1)</t>
+    <r>
+      <t>loadScript(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>sntzm_final(3)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>, 84)</t>
+    </r>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=21; gotomainline=终局（下）_84</t>
@@ -799,7 +817,25 @@
     <t>一只黑色的飞蛾从这片黑暗中狼狈地飞出，在带起一阵腥甜的气流擦过你的脸颊，它歪歪扭扭撞地落在大卫的肩膀上，扑腾了好几下才重新稳住身形，像一根羽毛，或是一根尚未点燃的引信。</t>
   </si>
   <si>
-    <t>loadScript(盖亚之心（上）_3, 1)</t>
+    <r>
+      <t>loadScript(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>sntzm_gy(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>, 3)</t>
+    </r>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=54; gotomainline=盖亚之心（上）_3</t>
@@ -934,7 +970,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>盖亚之心（上）</t>
+      <t>sntzm_gy(1)</t>
     </r>
     <r>
       <rPr>
@@ -942,7 +978,7 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>_4, 1)</t>
+      <t>, 4)</t>
     </r>
   </si>
   <si>
@@ -3144,7 +3180,6 @@
       <c r="J12" t="s">
         <v>15</v>
       </c>
-      <c r="K12"/>
       <c r="L12" t="s">
         <v>49</v>
       </c>
@@ -3975,7 +4010,7 @@
       <c r="J34" t="s">
         <v>15</v>
       </c>
-      <c r="K34" t="s">
+      <c r="K34" s="3" t="s">
         <v>114</v>
       </c>
       <c r="L34" t="s">
@@ -5527,7 +5562,7 @@
       <c r="J75" t="s">
         <v>15</v>
       </c>
-      <c r="K75" t="s">
+      <c r="K75" s="3" t="s">
         <v>244</v>
       </c>
       <c r="L75" t="s">
@@ -5869,7 +5904,6 @@
       <c r="J84" t="s">
         <v>15</v>
       </c>
-      <c r="K84"/>
       <c r="L84" t="s">
         <v>46</v>
       </c>
